--- a/output/TEST_CLASSIC_add_age_at_diagnosis.xlsx
+++ b/output/TEST_CLASSIC_add_age_at_diagnosis.xlsx
@@ -469,10 +469,10 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">1995-12-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-24</t>
+    <t xml:space="preserve">1996-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-06</t>
   </si>
   <si>
     <t xml:space="preserve">2025-11-19 19:55:00</t>
@@ -550,2583 +550,2583 @@
     <t xml:space="preserve">IV</t>
   </si>
   <si>
-    <t xml:space="preserve">2019-02-18</t>
+    <t xml:space="preserve">2019-05-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1972-02-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-30 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-18 09:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-20 14:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-16 08:36:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-11 07:58:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">olsen@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:14:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does not have comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1968-12-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-28 18:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-15 18:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-06 11:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-28 03:36:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-16 14:36:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">knott@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:42:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incomplete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1946-05-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-06 16:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-26 12:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-24 01:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-06 14:42:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-31 02:53:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">garcia@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:30:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has, ,comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1951-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-07 09:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-13 01:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-05 14:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-25 13:38:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-13 19:33:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cain@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
   </si>
   <si>
     <t xml:space="preserve">2020-10-03</t>
   </si>
   <si>
-    <t xml:space="preserve">Complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1971-11-26</t>
+    <t xml:space="preserve">2022-03-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1997-12-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-15 17:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-17 00:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-01 08:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-23 18:04:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-09 09:25:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zusi@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:28:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1981-02-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-23 16:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-23 19:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-14 18:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-26 15:36:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-04 00:04:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldman@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:20:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1981-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-06 11:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-07 08:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-09 08:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-19 00:33:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-11 19:40:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rogers@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:46:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1963-12-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-06 21:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-25 06:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-28 05:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-10 07:19:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-30 05:36:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brookshire@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:32:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has,comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-01-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-08-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1942-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-24 04:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-28 00:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-09 16:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-06 09:41:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-14 10:51:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pouliot@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:45:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1932-01-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-13 15:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-15 07:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-07 14:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-28 15:29:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-02 01:06:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">badgett@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:30:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1971-04-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-11 16:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-07 22:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-29 07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-13 16:45:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-13 20:01:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">schlortt@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:06:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1941-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-08 17:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-03 07:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-08 02:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-09 11:02:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-23 16:17:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wilson@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:52:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-07-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1925-12-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-29 21:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-25 20:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-01 23:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-22 01:57:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-03 14:49:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gale@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-01-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1926-03-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-17 05:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-19 21:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-20 06:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-20 02:55:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-18 16:43:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spears@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:10:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1960-03-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-31 19:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-25 16:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-28 03:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-10 07:36:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-29 21:46:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pannunzio@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:08:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1924-11-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-22 14:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-08 08:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-01 04:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-26 00:12:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-18 12:30:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archer@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:12:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-11-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-14 18:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-24 17:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-22 12:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-25 09:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-05 03:52:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trekell@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:04:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1920-03-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-22 03:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-24 11:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-23 05:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-16 12:27:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-24 14:56:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rausch@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:38:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-05-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1934-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-25 00:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-31 20:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-11 02:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-07 09:58:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-15 01:06:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">schmitz@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:18:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1957-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-24 02:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-28 14:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-16 22:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-12 03:24:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-19 18:33:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defrees@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02:33:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1921-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-15 16:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-03 01:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-20 20:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-20 04:02:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-09 18:20:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weir@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:48:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1963-11-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-15 19:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-02 01:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-15 21:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-18 13:29:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-04 20:01:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">niederhoff@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1956-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-18 10:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-28 19:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-12 18:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-20 02:27:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-23 16:34:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jarrett@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:55:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1965-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-18 21:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-11 10:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-14 06:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-11 00:42:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-18 13:31:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talbot@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:25:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1941-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-27 18:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-03 12:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-28 18:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-10 02:19:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-05 18:06:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ramovic@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:47:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1991-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-24 13:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-03 17:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-16 17:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-08 06:36:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-31 20:45:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weaver@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:16:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1982-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-21 11:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-21 12:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-20 05:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-20 23:18:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-18 00:57:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quaglieri@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:22:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-05-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-03-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1922-12-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-10 01:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-07 06:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-11 22:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-26 16:12:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-01 19:01:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">morris@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:50:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1944-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-20 19:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-12 21:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-26 18:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-27 14:40:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-17 03:39:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deplato@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:22:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1941-03-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-05 10:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-30 10:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-17 07:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-11 00:10:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-26 21:55:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gacesa@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:50:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1940-05-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-27 07:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-06 12:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-24 17:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-03 16:55:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-29 10:12:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fuller@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:19:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1971-02-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-19 04:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-20 03:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-13 04:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-07 07:40:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-01 12:40:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whisenhunt@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:52:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1935-12-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-15 23:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-21 11:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-06 01:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-05 02:37:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-02 10:06:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruse@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:54:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1982-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-02 22:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-06 02:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-23 21:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-12 02:14:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-22 00:11:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chance@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:48:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1953-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-28 01:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-08 19:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-29 18:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-21 06:16:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-29 13:32:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goemmer@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:46:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-11-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1967-01-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-09 02:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-14 22:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-25 19:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-21 04:15:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-22 11:36:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tucker@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:51:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-11-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1931-12-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-21 01:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-03 12:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-19 02:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-31 17:02:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-24 00:36:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hanenberg@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:51:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-02-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1995-12-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-16 09:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-07 01:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-13 10:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-26 07:16:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-17 14:06:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reed@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:42:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-03-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1957-04-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-18 22:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-30 12:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-23 12:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-05 18:58:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-10 07:40:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leasure@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:08:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-07-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-02-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1948-02-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-28 06:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-29 16:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-18 06:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-08 04:21:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-07 14:42:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rudder@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:42:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1964-02-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-28 22:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-02 05:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-09 11:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-07 09:20:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-21 22:10:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sharpe@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:48:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-02-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1957-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-27 03:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-07 19:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-12 05:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-04 00:40:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-02 22:07:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mainridge@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:14:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-02-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-12-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1938-03-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-09</t>
   </si>
   <si>
     <t xml:space="preserve">2024-04-28</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-06-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-30 15:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-18 09:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-20 14:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-16 08:36:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-11 07:58:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">olsen@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:14:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:11:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does not have comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1968-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-28 18:49:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-15 18:55:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-06 11:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-28 03:36:58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-16 14:36:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">knott@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:42:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00:50:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incomplete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-05-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1946-02-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-06 16:49:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-26 12:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-24 01:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-06 14:42:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-31 02:53:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">garcia@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:30:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:31:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has, ,comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1951-04-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-07 09:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-13 01:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-05 14:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-25 13:38:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-13 19:33:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cain@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:55:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1997-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-15 17:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-17 00:09:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-01 08:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-23 18:04:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-09 09:25:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zusi@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:28:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1980-11-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-23 16:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-23 19:06:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-14 18:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-26 15:36:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-04 00:04:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldman@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:20:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-09-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1981-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-06 11:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-07 08:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-09 08:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-19 00:33:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-11 19:40:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rogers@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:46:31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:47:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-05-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1963-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-06 21:55:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-25 06:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-28 05:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-10 07:19:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-30 05:36:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brookshire@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:32:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has,comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1942-05-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-24 04:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-28 00:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-09 16:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-06 09:41:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-14 10:51:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pouliot@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:45:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-12-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1931-11-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-13 15:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-15 07:36:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-07 14:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-28 15:29:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-02 01:06:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">badgett@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:30:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-03-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1971-01-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-11 16:05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-07 22:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-29 07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-13 16:45:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-13 20:01:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">schlortt@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:06:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1941-04-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-08 17:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-03 07:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-08 02:58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-09 11:02:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-23 16:17:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wilson@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:52:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1925-09-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-29 21:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-25 20:41:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-01 23:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-22 01:57:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-03 14:49:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gale@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-11-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1925-12-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-17 05:55:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-19 21:45:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-20 06:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-20 02:55:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-18 16:43:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spears@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:10:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-05-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1960-01-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-31 19:02:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-25 16:35:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-28 03:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-10 07:36:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-29 21:46:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pannunzio@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:08:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:31:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-12-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1924-08-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-22 14:45:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-08 08:52:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-01 04:31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-26 00:12:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-18 12:30:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archer@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:12:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000-06-25</t>
+    <t xml:space="preserve">2024-11-05 10:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-06 19:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-02 23:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-10 07:41:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-29 20:02:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turner@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:12:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1948-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">2024-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-12-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-14 18:01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-24 17:29:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-22 12:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-25 09:15:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-05 03:52:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trekell@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:04:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1920-01-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-22 03:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-24 11:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-23 05:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-16 12:27:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-24 14:56:47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rausch@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:38:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-11-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1934-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-25 00:25:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-31 20:49:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-11 02:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-07 09:58:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-15 01:06:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">schmitz@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:18:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:47:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1957-06-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-24 02:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-28 14:10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-16 22:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-12 03:24:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-19 18:33:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defrees@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02:33:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02:47:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-03-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1921-08-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-15 16:24:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-03 01:52:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-20 20:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-20 04:02:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-09 18:20:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weir@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:48:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-04-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1963-08-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-15 19:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-02 01:50:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-15 21:14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-18 13:29:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-04 20:01:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">niederhoff@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1956-04-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-18 10:16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-28 19:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-12 18:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-20 02:27:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-23 16:34:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jarrett@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:55:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:11:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-03-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-05-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1965-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-18 21:40:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-11 10:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-14 06:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-11 00:42:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18 13:31:57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talbot@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:25:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:56:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1941-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-27 18:04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-03 12:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-28 18:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-10 02:19:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-05 18:06:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ramovic@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00:47:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1991-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-24 13:38:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-03 17:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-16 17:11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-08 06:36:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-31 20:45:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weaver@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:16:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:23:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1982-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-21 11:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-21 12:19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-20 05:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-20 23:18:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-18 00:57:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quaglieri@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:22:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-02-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1922-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-10 01:04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-07 06:29:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-11 22:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-26 16:12:41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-01 19:01:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">morris@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:50:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1944-03-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-20 19:01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-12 21:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-26 18:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-27 14:40:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-17 03:39:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deplato@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:22:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-05-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1941-01-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-05 10:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-30 10:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-17 07:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-11 00:10:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-26 21:55:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gacesa@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:50:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:45:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1940-02-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-27 07:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-06 12:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-24 17:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-03 16:55:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-29 10:12:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fuller@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:19:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1970-12-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-20</t>
+    <t xml:space="preserve">2024-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-03 12:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-17 18:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-11 22:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-16 14:28:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-21 02:38:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snyder@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:43:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-12-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1941-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-01 11:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-03 03:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-12 10:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-22 01:31:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-08 06:55:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">killingsworth@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:59:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1940-05-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-16 00:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-11 10:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-15 18:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-13 13:12:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-31 07:51:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duerksen@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:04:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1923-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-26 12:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-18 20:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-08 22:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-20 11:53:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-27 01:15:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nemeth@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:47:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1970-01-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-24 18:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-20 18:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-13 22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-17 13:49:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-09 08:27:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clark@fakemail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:26:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-01-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1922-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-30</t>
   </si>
   <si>
     <t xml:space="preserve">2024-09-21</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-01-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-19 04:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-20 03:51:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-13 04:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-07 07:40:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-01 12:40:08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whisenhunt@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:52:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1935-09-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-15 23:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-21 11:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-06 01:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-05 02:37:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-02 10:06:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ruse@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:54:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1982-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-02 22:15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-06 02:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-23 21:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-12 02:14:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-22 00:11:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chance@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:48:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1953-05-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-28 01:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-08 19:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-29 18:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-21 06:16:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-29 13:32:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goemmer@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:46:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-08-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1966-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-09 02:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-14 22:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-25 19:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-21 04:15:57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-22 11:36:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tucker@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:51:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-04-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1931-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-21 01:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-03 12:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-19 02:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-31 17:02:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-24 00:36:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hanenberg@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:51:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-12-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1995-10-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-16 09:12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-07 01:26:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-13 10:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-26 07:16:14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-17 14:06:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reed@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:42:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1957-02-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-18 22:10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-30 12:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-23 12:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-05 18:58:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-10 07:40:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leasure@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:08:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-05-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-11-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1947-12-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-28 06:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-29 16:19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18 06:11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-08 04:21:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-07 14:42:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rudder@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:42:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1963-11-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-28 22:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-02 05:59:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-09 11:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-07 09:20:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-21 22:10:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sharpe@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:48:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:13:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-11-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1957-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-27 03:35:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-07 19:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-12 05:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-04 00:40:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-02 22:07:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mainridge@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:14:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:25:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-11-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1937-12-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-05 10:56:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-06 19:19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-02 23:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-10 07:41:58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-29 20:02:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turner@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:12:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:52:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-12-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1948-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-03 12:26:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-17 18:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-11 22:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-16 14:28:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-21 02:38:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snyder@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:43:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028-10-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1941-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-01 11:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-03 03:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-12 10:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-22 01:31:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-08 06:55:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">killingsworth@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:59:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-03-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1940-02-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-16 00:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-11 10:05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-15 18:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-13 13:12:31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-31 07:51:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">duerksen@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:04:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1923-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-26 12:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18 20:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-08 22:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-20 11:53:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-27 01:15:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nemeth@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:47:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1969-11-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-24 18:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-20 18:29:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-13 22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-17 13:49:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-09 08:27:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clark@fakemail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:26:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-11-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-02-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1922-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024-04-27 17:59:00</t>
   </si>
   <si>
@@ -3157,10 +3157,10 @@
     <t xml:space="preserve">117</t>
   </si>
   <si>
-    <t xml:space="preserve">2020-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-08-20</t>
+    <t xml:space="preserve">2020-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-02</t>
   </si>
   <si>
     <t xml:space="preserve">form_name</t>
@@ -4024,7 +4024,7 @@
     <t xml:space="preserve">last_save_time</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-06 08:05:22.524107</t>
+    <t xml:space="preserve">2026-05-10 15:19:34.269017</t>
   </si>
   <si>
     <t xml:space="preserve">final_form_tab_names</t>
